--- a/Data/GP2_BODYWEIGHT.xlsx
+++ b/Data/GP2_BODYWEIGHT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Guinea-Pig-data_2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E67A55-D03D-430C-86FF-35C15AF94524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3219E8-EC67-42A9-8CD8-70E9B9A14E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BC909284-01A5-4060-BFAF-EA7D13221CD6}"/>
   </bookViews>
@@ -455,7 +455,9 @@
   <dimension ref="A1:G794"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="5" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="8.7265625" style="1"/>
+    <col min="2" max="2" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="8.7265625" style="1"/>
     <col min="6" max="6" width="13.90625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.1796875" style="1" bestFit="1" customWidth="1"/>
   </cols>
